--- a/DataDriven/absensi.xlsx
+++ b/DataDriven/absensi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aldopriamnistikogmail.com/Projects/Project_Automation_RobotFramework_StarAsiaPerkasa/DataDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D030701B-C0D1-E647-B84F-DD7584065468}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BB6E27-97DA-1842-8D53-9D4D3A3C2DEB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="660" windowWidth="28040" windowHeight="17020" xr2:uid="{660C6164-87BB-604E-90F2-913DC4C4E1DB}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>Search_lokasi_kerja</t>
   </si>
@@ -106,24 +106,22 @@
   </si>
   <si>
     <t>YOGA SETYA PUTRA</t>
+  </si>
+  <si>
+    <t>Workshop</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="-webkit-standard"/>
     </font>
     <font>
       <sz val="12"/>
@@ -152,14 +150,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -477,13 +474,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03DCB35B-5DF9-2349-816F-2347BD3F7B7C}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="11" max="11" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -527,9 +524,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>14</v>
@@ -568,11 +565,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="34">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
@@ -607,7 +606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="17">
+    <row r="4" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
